--- a/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
@@ -1076,11 +1076,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -1107,11 +1105,9 @@
 8:53</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
@@ -1147,11 +1143,9 @@
 8:52</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
@@ -1170,11 +1164,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -1193,18 +1185,14 @@
 8:35</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1240,18 +1228,14 @@
 9:56</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
@@ -1314,18 +1298,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -1344,18 +1324,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
@@ -1390,11 +1366,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1421,18 +1395,14 @@
 8:32</t>
         </is>
       </c>
-      <c r="S8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
@@ -1468,11 +1438,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z8" s="1" t="inlineStr">
@@ -1493,10 +1461,10 @@
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>21:30
 DTT1
-17:00
-8:00</t>
+31:30
+10:00</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1507,11 +1475,9 @@
 9:42</t>
         </is>
       </c>
-      <c r="AD8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -1534,18 +1500,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -1574,16 +1536,15 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+          <t>5:22
+CD0078
+13:47
+8:25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
@@ -1602,11 +1563,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
@@ -1633,11 +1592,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr">
@@ -1680,32 +1637,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA9" s="1" t="inlineStr">
@@ -1776,18 +1725,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
@@ -1823,18 +1768,14 @@
 9:22</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -1877,11 +1818,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="S10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr">
@@ -1908,18 +1847,14 @@
 8:10</t>
         </is>
       </c>
-      <c r="W10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y10" s="1" t="inlineStr">
@@ -1938,11 +1873,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB10" s="1" t="inlineStr">
@@ -1961,11 +1894,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -1980,11 +1911,9 @@
           <t>陳明裕</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -2027,11 +1956,9 @@
 8:24</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
@@ -2058,11 +1985,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -2081,11 +2006,9 @@
 9:01</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q11" s="1" t="inlineStr">
@@ -2120,18 +2043,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="U11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W11" s="1" t="inlineStr">
@@ -2167,11 +2086,9 @@
 9:06</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB11" s="1" t="inlineStr">
@@ -2190,11 +2107,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -2209,11 +2124,9 @@
           <t>許治偉</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -2256,11 +2169,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
@@ -2303,18 +2214,14 @@
 8:55</t>
         </is>
       </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
@@ -2333,18 +2240,14 @@
 9:32</t>
         </is>
       </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U12" s="1" t="inlineStr">
@@ -2388,11 +2291,9 @@
 8:35</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA12" s="1" t="inlineStr">
@@ -2419,11 +2320,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -2454,19 +2353,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>11:53
-CD0085
-20:17
-8:24</t>
+          <t>13:03
+CD0506
+21:03
+8:00</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -2485,11 +2382,9 @@
 8:18</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
@@ -2516,11 +2411,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2539,11 +2432,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q13" s="1" t="inlineStr">
@@ -2562,11 +2453,9 @@
 9:15</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr">
@@ -2585,11 +2474,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W13" s="1" t="inlineStr">
@@ -2611,9 +2498,9 @@
       </c>
       <c r="Y13" s="1" t="inlineStr">
         <is>
-          <t>4:00
-STD1
-12:00
+          <t>9:33
+CD0055
+17:33
 8:00</t>
         </is>
       </c>
@@ -2625,18 +2512,14 @@
 8:38</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
@@ -2691,18 +2574,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
@@ -2730,18 +2609,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -2776,18 +2651,14 @@
 9:23</t>
         </is>
       </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S14" s="1" t="inlineStr">
@@ -2830,18 +2701,14 @@
 8:25</t>
         </is>
       </c>
-      <c r="X14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z14" s="1" t="inlineStr">
@@ -2868,11 +2735,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
@@ -2919,11 +2784,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -2942,25 +2805,19 @@
 8:13</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -3003,11 +2860,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr">
@@ -3050,18 +2905,14 @@
 8:45</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y15" s="1" t="inlineStr">
@@ -3104,11 +2955,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3123,11 +2972,9 @@
           <t>湯逢吉</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -3146,11 +2993,9 @@
 9:59</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -3178,11 +3023,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
@@ -3225,18 +3068,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr">
@@ -3279,11 +3118,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X16" s="1" t="inlineStr">
@@ -3327,18 +3164,14 @@
 8:42</t>
         </is>
       </c>
-      <c r="AC16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3377,18 +3210,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -3416,11 +3245,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -3447,11 +3274,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -3470,18 +3295,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr">
@@ -3516,11 +3337,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y17" s="1" t="inlineStr">
@@ -3547,11 +3366,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="AB17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
@@ -3598,11 +3415,9 @@
 9:05</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -3629,25 +3444,19 @@
 8:57</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -3690,18 +3499,14 @@
 8:12</t>
         </is>
       </c>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="S18" s="1" t="inlineStr">
@@ -3736,18 +3541,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y18" s="1" t="inlineStr">
@@ -3758,18 +3559,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB18" s="1" t="inlineStr">
@@ -3832,18 +3629,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
@@ -3871,18 +3664,14 @@
 8:45</t>
         </is>
       </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M19" s="1" t="inlineStr">
@@ -3917,18 +3706,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr">
@@ -3971,11 +3756,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y19" s="1" t="inlineStr">
@@ -4010,11 +3793,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD19" s="1" t="inlineStr">
@@ -4053,18 +3834,14 @@
 8:16</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
@@ -4100,11 +3877,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -4139,11 +3914,9 @@
 8:19</t>
         </is>
       </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
@@ -4162,11 +3935,9 @@
 8:42</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
@@ -4185,11 +3956,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W20" s="1" t="inlineStr">
@@ -4209,11 +3978,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="Y20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
@@ -4248,11 +4015,9 @@
 9:01</t>
         </is>
       </c>
-      <c r="AD20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -4275,11 +4040,9 @@
 8:33</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -4314,18 +4077,14 @@
 8:19</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
@@ -4377,11 +4136,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
@@ -4424,11 +4181,9 @@
 8:57</t>
         </is>
       </c>
-      <c r="W21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X21" s="1" t="inlineStr">
@@ -4456,11 +4211,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB21" s="1" t="inlineStr">
@@ -4479,11 +4232,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -4522,18 +4273,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
@@ -4577,26 +4324,22 @@
 8:00</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>6:49
-CD0082
-14:49
-8:00</t>
+          <t>4:15
+CD0023
+12:59
+8:44</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -4607,11 +4350,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr">
@@ -4646,11 +4387,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr">
@@ -4672,32 +4411,28 @@
       </c>
       <c r="Y22" s="1" t="inlineStr">
         <is>
-          <t>7:59
-CD0042
-17:37
-9:38</t>
+          <t>4:10
+CD0031
+13:52
+9:42</t>
         </is>
       </c>
       <c r="Z22" s="1" t="inlineStr">
         <is>
-          <t>6:53
-CD0032
-14:53
-8:00</t>
-        </is>
-      </c>
-      <c r="AA22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>4:15
+CD0061
+13:15
+9:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC22" s="1" t="inlineStr">
@@ -4752,18 +4487,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
@@ -4799,18 +4530,14 @@
 9:32</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -4845,11 +4572,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
@@ -4884,18 +4609,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y23" s="1" t="inlineStr">
@@ -4938,11 +4659,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="AD23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -4957,11 +4676,9 @@
           <t>陳建志</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -4996,25 +4713,19 @@
 8:32</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
@@ -5057,11 +4768,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -5080,18 +4789,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U24" s="1" t="inlineStr">
@@ -5135,11 +4840,9 @@
 9:33</t>
         </is>
       </c>
-      <c r="Z24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA24" s="1" t="inlineStr">
@@ -5166,11 +4869,9 @@
 8:57</t>
         </is>
       </c>
-      <c r="AD24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -5201,18 +4902,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
@@ -5240,11 +4937,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
@@ -5271,11 +4966,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -5318,11 +5011,9 @@
 8:21</t>
         </is>
       </c>
-      <c r="T25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U25" s="1" t="inlineStr">
@@ -5341,11 +5032,9 @@
 8:30</t>
         </is>
       </c>
-      <c r="W25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X25" s="1" t="inlineStr">
@@ -5365,18 +5054,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB25" s="1" t="inlineStr">
@@ -5423,11 +5108,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -5462,11 +5145,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
@@ -5501,18 +5182,14 @@
 8:42</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -5539,18 +5216,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -5586,11 +5259,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z26" s="1" t="inlineStr">
@@ -5625,11 +5296,9 @@
 8:09</t>
         </is>
       </c>
-      <c r="AD26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -5652,11 +5321,9 @@
 8:13</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -5669,10 +5336,10 @@
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>13:03
-CD0506
-21:03
-8:00</t>
+          <t>11:53
+CD0085
+20:17
+8:24</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
@@ -5691,11 +5358,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
@@ -5722,18 +5387,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -5776,18 +5437,14 @@
 8:59</t>
         </is>
       </c>
-      <c r="T27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V27" s="1" t="inlineStr">
@@ -5831,18 +5488,14 @@
 9:36</t>
         </is>
       </c>
-      <c r="AA27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC27" s="1" t="inlineStr">
@@ -5897,11 +5550,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
@@ -5912,11 +5563,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
@@ -5936,11 +5585,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -5975,25 +5622,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S28" s="1" t="inlineStr">
@@ -6036,27 +5677,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="X28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y28" s="1" t="inlineStr">
         <is>
-          <t>4:10
-CD0031
-13:52
-9:42</t>
+          <t>7:59
+CD0042
+17:37
+9:38</t>
         </is>
       </c>
       <c r="Z28" s="1" t="inlineStr">
         <is>
-          <t>4:15
-CD0061
-13:15
-9:00</t>
+          <t>6:53
+CD0032
+14:53
+8:00</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
@@ -6077,17 +5716,15 @@
       </c>
       <c r="AC28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="AD28" s="1" t="inlineStr">
-        <is>
-          <t>3:59
-CD0013
-12:35
-8:36</t>
+          <t>14:55
+CD0557
+22:55
+8:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6102,11 +5739,9 @@
           <t>田景耀</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -6133,11 +5768,9 @@
 9:21</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
@@ -6165,11 +5798,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -6198,17 +5829,15 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>4:15
-CD0023
-12:59
-8:44</t>
-        </is>
-      </c>
-      <c r="P29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>6:49
+CD0082
+14:49
+8:00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
@@ -6227,11 +5856,9 @@
 9:05</t>
         </is>
       </c>
-      <c r="S29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T29" s="1" t="inlineStr">
@@ -6258,25 +5885,21 @@
 8:00</t>
         </is>
       </c>
-      <c r="W29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y29" s="1" t="inlineStr">
         <is>
-          <t>9:33
-CD0055
-17:33
+          <t>4:00
+STD1
+12:00
 8:00</t>
         </is>
       </c>
@@ -6304,19 +5927,17 @@
 8:55</t>
         </is>
       </c>
-      <c r="AC29" s="1" t="inlineStr">
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD29" s="1" t="inlineStr">
         <is>
           <t>3:59
-CD0007
-12:40
-8:41</t>
-        </is>
-      </c>
-      <c r="AD29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+CD0086
+11:59
+8:00</t>
         </is>
       </c>
     </row>
@@ -6331,11 +5952,9 @@
           <t>謝宗宏</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -6370,25 +5989,19 @@
 9:53</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -6407,11 +6020,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N30" s="1" t="inlineStr">
@@ -6454,11 +6065,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T30" s="1" t="inlineStr">
@@ -6485,11 +6094,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X30" s="1" t="inlineStr">
@@ -6517,12 +6124,9 @@
 8:44</t>
         </is>
       </c>
-      <c r="AA30" s="1" t="inlineStr">
-        <is>
-          <t>4:00
-STD1
-12:00
-8:00</t>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB30" s="1" t="inlineStr">
@@ -6535,16 +6139,15 @@
       </c>
       <c r="AC30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>5:22
+CD0077
+13:40
+8:18</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6559,11 +6162,9 @@
           <t>簡榮逸</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -6598,11 +6199,9 @@
 8:41</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
@@ -6638,11 +6237,9 @@
 9:41</t>
         </is>
       </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N31" s="1" t="inlineStr">
@@ -6670,11 +6267,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr">
@@ -6701,11 +6296,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V31" s="1" t="inlineStr">
@@ -6749,18 +6342,14 @@
 8:20</t>
         </is>
       </c>
-      <c r="AA31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC31" s="1" t="inlineStr">
@@ -6799,11 +6388,9 @@
 8:35</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -6830,11 +6417,9 @@
 8:21</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
@@ -6854,11 +6439,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -6893,11 +6476,9 @@
 9:02</t>
         </is>
       </c>
-      <c r="P32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q32" s="1" t="inlineStr">
@@ -6924,18 +6505,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V32" s="1" t="inlineStr">
@@ -6971,11 +6548,9 @@
 8:23</t>
         </is>
       </c>
-      <c r="Z32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA32" s="1" t="inlineStr">
@@ -6994,19 +6569,17 @@
 8:03</t>
         </is>
       </c>
-      <c r="AC32" s="1" t="inlineStr">
-        <is>
-          <t>14:55
-CD0557
-22:55
-8:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>3:59
+CD0013
+12:35
+8:36</t>
         </is>
       </c>
     </row>
@@ -7021,14 +6594,99 @@
           <t>楊心喬</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>DO3W
+NGRSN</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>DO2W
+DO2WDO2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7036,7 +6694,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="S33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7044,7 +6702,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="T33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7052,7 +6710,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="U33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7060,7 +6718,25 @@
 9:00</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="V33" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+NGRSD
+17:30
+9:00</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y33" s="1" t="inlineStr">
         <is>
           <t>8:30
 DO3W
@@ -7069,77 +6745,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>5:22
-DO2W
-CD0078
-13:47
-8:25</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R33" s="1" t="inlineStr">
+      <c r="Z33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7147,7 +6753,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="S33" s="1" t="inlineStr">
+      <c r="AA33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7155,7 +6761,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="T33" s="1" t="inlineStr">
+      <c r="AB33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7163,7 +6769,7 @@
 9:00</t>
         </is>
       </c>
-      <c r="U33" s="1" t="inlineStr">
+      <c r="AC33" s="1" t="inlineStr">
         <is>
           <t>8:30
 NGRSD
@@ -7171,74 +6777,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="V33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="W33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DO3W
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="Z33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="AA33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="AB33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="AC33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-NGRSD
-17:30
-9:00</t>
-        </is>
-      </c>
-      <c r="AD33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
     </row>
@@ -7261,11 +6802,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -7300,11 +6839,9 @@
 8:37</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
@@ -7315,11 +6852,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -7354,18 +6889,14 @@
 8:55</t>
         </is>
       </c>
-      <c r="P34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R34" s="1" t="inlineStr">
@@ -7408,11 +6939,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="W34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X34" s="1" t="inlineStr">
@@ -7432,18 +6961,14 @@
 8:33</t>
         </is>
       </c>
-      <c r="Z34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
@@ -7498,18 +7023,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -7561,11 +7082,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N35" s="1" t="inlineStr">
@@ -7584,11 +7103,9 @@
 8:09</t>
         </is>
       </c>
-      <c r="P35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q35" s="1" t="inlineStr">
@@ -7623,18 +7140,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="U35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W35" s="1" t="inlineStr">
@@ -7670,18 +7183,14 @@
 9:07</t>
         </is>
       </c>
-      <c r="AA35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC35" s="1" t="inlineStr">
@@ -7720,11 +7229,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -7743,11 +7250,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
@@ -7793,16 +7298,15 @@
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>6:49
+CD0079
+14:49
+8:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -7821,11 +7325,9 @@
 8:23</t>
         </is>
       </c>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R36" s="1" t="inlineStr">
@@ -7844,11 +7346,9 @@
 9:41</t>
         </is>
       </c>
-      <c r="T36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
@@ -7892,18 +7392,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB36" s="1" t="inlineStr">
@@ -7974,18 +7470,14 @@
 8:57</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr">
@@ -8013,18 +7505,14 @@
 9:02</t>
         </is>
       </c>
-      <c r="L37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N37" s="1" t="inlineStr">
@@ -8059,11 +7547,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S37" s="1" t="inlineStr">
@@ -8098,18 +7584,14 @@
 8:35</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y37" s="1" t="inlineStr">
@@ -8130,9 +7612,10 @@
       </c>
       <c r="AA37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO1
-</t>
+          <t>4:00
+STD1
+12:00
+8:00</t>
         </is>
       </c>
       <c r="AB37" s="1" t="inlineStr">
@@ -8143,19 +7626,14 @@
 9:00</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
-        <is>
-          <t>5:22
-CD0077
-13:40
-8:18</t>
-        </is>
-      </c>
-      <c r="AD37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -8170,11 +7648,9 @@
           <t>林威丞</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -8209,11 +7685,9 @@
 8:19</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I38" s="1" t="inlineStr">
@@ -8241,18 +7715,16 @@
 8:04</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M38" s="1" t="inlineStr">
         <is>
-          <t>6:49
-CD0079
-14:49
+          <t>8:30
+FAC
+17:30
 8:00</t>
         </is>
       </c>
@@ -8272,11 +7744,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q38" s="1" t="inlineStr">
@@ -8311,18 +7781,14 @@
 9:59</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W38" s="1" t="inlineStr">
@@ -8350,11 +7816,9 @@
 9:27</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA38" s="1" t="inlineStr">
@@ -8373,11 +7837,9 @@
 10:00</t>
         </is>
       </c>
-      <c r="AC38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD38" s="1" t="inlineStr">
@@ -8400,11 +7862,9 @@
           <t>賴裕昊</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -8439,11 +7899,9 @@
 8:37</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr">
@@ -8463,11 +7921,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr">
@@ -8502,11 +7958,9 @@
 8:05</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q39" s="1" t="inlineStr">
@@ -8541,18 +7995,14 @@
 8:57</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W39" s="1" t="inlineStr">
@@ -8596,18 +8046,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD39" s="1" t="inlineStr">
@@ -8630,11 +8076,9 @@
           <t>林晏如</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -8669,11 +8113,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
@@ -8693,11 +8135,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L40" s="1" t="inlineStr">
@@ -8732,18 +8172,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr">
@@ -8770,11 +8206,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V40" s="1" t="inlineStr">
@@ -8802,11 +8236,9 @@
 9:07</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z40" s="1" t="inlineStr">
@@ -8841,11 +8273,9 @@
 8:55</t>
         </is>
       </c>
-      <c r="AD40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -8876,18 +8306,14 @@
 9:37</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -8923,11 +8349,9 @@
 8:28</t>
         </is>
       </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L41" s="1" t="inlineStr">
@@ -8962,11 +8386,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q41" s="1" t="inlineStr">
@@ -8985,18 +8407,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U41" s="1" t="inlineStr">
@@ -9032,11 +8450,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="Y41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z41" s="1" t="inlineStr">
@@ -9065,17 +8481,15 @@
       </c>
       <c r="AC41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="AD41" s="1" t="inlineStr">
-        <is>
           <t>3:59
-CD0086
-11:59
-8:00</t>
+CD0007
+12:40
+8:41</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -9122,18 +8536,14 @@
 8:04</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
@@ -9153,11 +8563,9 @@
 8:33</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -9184,11 +8592,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr">
@@ -9225,24 +8631,20 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>8:30
 M
-16:00
-8:00</t>
-        </is>
-      </c>
-      <c r="U42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W42" s="1" t="inlineStr">
@@ -9262,11 +8664,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z42" s="1" t="inlineStr">
@@ -9301,11 +8701,9 @@
 8:19</t>
         </is>
       </c>
-      <c r="AD42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -9328,18 +8726,14 @@
 8:36</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -9383,11 +8777,9 @@
 8:24</t>
         </is>
       </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L43" s="1" t="inlineStr">
@@ -9422,18 +8814,14 @@
 8:41</t>
         </is>
       </c>
-      <c r="P43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R43" s="1" t="inlineStr">
@@ -9452,11 +8840,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="T43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U43" s="1" t="inlineStr">
@@ -9492,11 +8878,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z43" s="1" t="inlineStr">
@@ -9531,11 +8915,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -9550,11 +8932,9 @@
           <t>林慰捷</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -9589,11 +8969,9 @@
 9:41</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
@@ -9613,11 +8991,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -9644,11 +9020,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -9667,11 +9041,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S44" s="1" t="inlineStr">
@@ -9698,11 +9070,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W44" s="1" t="inlineStr">
@@ -9738,18 +9108,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC44" s="1" t="inlineStr">

--- a/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
@@ -1459,12 +1459,9 @@
 9:36</t>
         </is>
       </c>
-      <c r="AB8" s="1" t="inlineStr">
-        <is>
-          <t>21:30
-DTT1
-31:30
-10:00</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1492,12 +1489,9 @@
           <t>王勝學</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1701,28 +1695,19 @@
           <t>陳炯良</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1865,12 +1850,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z10" s="1" t="inlineStr">
-        <is>
-          <t>8:00
-DTT1
-17:00
-8:00</t>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2053,12 +2035,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr">
@@ -2091,12 +2070,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2296,28 +2272,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2768,20 +2735,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2820,12 +2781,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="M15" s="1" t="inlineStr">
@@ -2865,12 +2823,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="S15" s="1" t="inlineStr">
@@ -2889,12 +2844,9 @@
 8:33</t>
         </is>
       </c>
-      <c r="U15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
@@ -3202,12 +3154,9 @@
 8:42</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3250,12 +3199,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
@@ -3313,12 +3259,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V17" s="1" t="inlineStr">
@@ -3509,36 +3452,24 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="S18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -3551,12 +3482,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3569,20 +3497,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>LUTS</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="AD18" s="1" t="inlineStr">
@@ -3605,28 +3527,19 @@
           <t>陳柏希</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3983,20 +3896,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="AB20" s="1" t="inlineStr">
@@ -4149,12 +4056,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S21" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr">
@@ -4773,20 +4677,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -4886,20 +4784,14 @@
           <t>葉寶峰</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4912,12 +4804,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
@@ -5555,12 +5444,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>FAC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5773,12 +5659,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
@@ -5803,12 +5686,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M29" s="1" t="inlineStr">
@@ -6636,44 +6516,29 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -6844,12 +6709,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -6899,12 +6761,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S34" s="1" t="inlineStr">
@@ -7074,12 +6933,9 @@
 8:42</t>
         </is>
       </c>
-      <c r="L35" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -7087,12 +6943,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="N35" s="1" t="inlineStr">
-        <is>
-          <t>8:00
-DTT1
-17:00
-8:00</t>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -7720,20 +7573,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="M38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>FAC</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -7829,12 +7676,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
-        <is>
-          <t>21:30
-DTT1
-31:30
-10:00</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -8164,12 +8008,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -8182,20 +8023,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S40" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T40" s="1" t="inlineStr">

--- a/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
@@ -1073,7 +1073,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1086,7 +1086,7 @@
           <t>17:25
 CD0852
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -1094,7 +1094,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -1102,7 +1102,7 @@
           <t>15:53
 CD5903
 24:46
-8:53</t>
+08:53</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1116,7 +1116,7 @@
 DO2W
 CD0573
 25:07
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
@@ -1124,7 +1124,7 @@
           <t>17:01
 CD0574
 25:01
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
@@ -1132,7 +1132,7 @@
           <t>16:22
 CD0554
 24:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -1140,7 +1140,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1153,7 +1153,7 @@
           <t>17:30
 CD0578
 25:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1161,7 +1161,7 @@
           <t>16:58
 CD0576
 25:30
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1174,7 +1174,7 @@
           <t>15:03
 CD0517
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr">
@@ -1182,7 +1182,7 @@
           <t>12:28
 CD0554
 21:03
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1197,35 +1197,35 @@
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0034
 13:54
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="V7" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W7" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0027
 14:35
-9:45</t>
+09:45</t>
         </is>
       </c>
       <c r="X7" s="1" t="inlineStr">
         <is>
-          <t>4:04
+          <t>04:04
 DO2W
 CD0057
 14:00
-9:56</t>
+09:56</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1240,34 +1240,34 @@
       </c>
       <c r="AA7" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AD7" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
           <t>17:25
 CD0579
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -1295,7 +1295,7 @@
           <t>17:11
 CD0543
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1313,7 +1313,7 @@
           <t>12:04
 CD0507
 20:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
@@ -1321,7 +1321,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1336,34 +1336,34 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0064
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>4:34
+          <t>04:34
 CD0033
 12:34
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1373,26 +1373,26 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0013
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0020
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1407,18 +1407,18 @@
       </c>
       <c r="U8" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0081
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V8" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="W8" s="1" t="inlineStr">
@@ -1426,16 +1426,16 @@
           <t>10:53
 CD5902
 19:03
-8:10</t>
+08:10</t>
         </is>
       </c>
       <c r="X8" s="1" t="inlineStr">
         <is>
-          <t>8:45
+          <t>08:45
 DO2W
 CD0046
 16:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1445,18 +1445,18 @@
       </c>
       <c r="Z8" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA8" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:35
-9:36</t>
+09:36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0074
 14:32
-9:42</t>
+09:42</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1506,34 +1506,34 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>6:09
+          <t>06:09
 CD0082
 14:09
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0078
 13:47
-8:25</t>
+08:25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1543,18 +1543,18 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0020
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1564,26 +1564,26 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0063
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0011
 12:37
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1593,42 +1593,42 @@
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0008
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="U9" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0063
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V9" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1656,7 +1656,7 @@
           <t>12:04
 CD0506
 20:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB9" s="1" t="inlineStr">
@@ -1664,7 +1664,7 @@
           <t>15:59
 CD0530
 24:50
-8:51</t>
+08:51</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -1672,7 +1672,7 @@
           <t>16:25
 CD0570
 24:50
-8:25</t>
+08:25</t>
         </is>
       </c>
       <c r="AD9" s="1" t="inlineStr">
@@ -1680,7 +1680,7 @@
           <t>16:05
 CD0569
 25:25
-9:20</t>
+09:20</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
           <t>17:11
 CD0531
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
@@ -1734,7 +1734,7 @@
 DO2W
 CD0567
 24:50
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
@@ -1742,7 +1742,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
@@ -1750,7 +1750,7 @@
           <t>14:59
 CD0559
 24:21
-9:22</t>
+09:22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1768,7 +1768,7 @@
           <t>17:04
 CD0577
 25:30
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1776,7 +1776,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1784,7 +1784,7 @@
           <t>15:45
 CD0567
 24:50
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
@@ -1792,7 +1792,7 @@
           <t>16:25
 CD0570
 25:00
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr">
@@ -1800,7 +1800,7 @@
           <t>17:04
 CD0543
 25:11
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1810,18 +1810,18 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U10" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V10" s="1" t="inlineStr">
@@ -1829,7 +1829,7 @@
           <t>13:53
 CD0509
 22:03
-8:10</t>
+08:10</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1847,7 +1847,7 @@
           <t>10:53
 CD0064
 18:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1862,18 +1862,18 @@
       </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1900,10 +1900,10 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -1911,15 +1911,15 @@
           <t>10:13
 CD0085
 19:18
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
@@ -1927,7 +1927,7 @@
           <t>11:45
 CD0052
 19:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
@@ -1935,7 +1935,7 @@
           <t>11:53
 CD0051
 20:17
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1945,26 +1945,26 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0065
 13:15
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1977,7 +1977,7 @@
           <t>11:48
 CD0054
 21:41
-9:53</t>
+09:53</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1985,7 +1985,7 @@
           <t>11:16
 CD0051
 20:17
-9:01</t>
+09:01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1995,34 +1995,34 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>8:45
+          <t>08:45
 CD0046
 16:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>5:02
+          <t>05:02
 CD0031
 14:08
-9:06</t>
+09:06</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2046,7 +2046,7 @@
 DO2W
 CD0544
 25:13
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="Y11" s="1" t="inlineStr">
@@ -2054,7 +2054,7 @@
           <t>16:25
 CD0554
 24:51
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="Z11" s="1" t="inlineStr">
@@ -2062,7 +2062,7 @@
           <t>13:16
 CD0506
 22:22
-9:06</t>
+09:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2080,7 +2080,7 @@
           <t>13:04
 CD0509
 21:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2107,42 +2107,42 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>5:02
+          <t>05:02
 CD0031
 14:08
-9:06</t>
+09:06</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>4:34
+          <t>04:34
 CD0811
 12:54
-8:20</t>
+08:20</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 13:20
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2152,42 +2152,42 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>6:59
+          <t>06:59
 CD5901
 15:06
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2202,18 +2202,18 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0035
 14:54
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2231,7 +2231,7 @@
           <t>16:53
 CD0541
 25:25
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="V12" s="1" t="inlineStr">
@@ -2239,7 +2239,7 @@
           <t>16:04
 CD5901
 25:00
-8:56</t>
+08:56</t>
         </is>
       </c>
       <c r="W12" s="1" t="inlineStr">
@@ -2247,7 +2247,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X12" s="1" t="inlineStr">
@@ -2256,7 +2256,7 @@
 DO2W
 CD0552
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y12" s="1" t="inlineStr">
@@ -2264,7 +2264,7 @@
           <t>16:45
 CD0568
 25:20
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2309,7 +2309,7 @@
           <t>10:59
 CD0050
 18:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -2317,7 +2317,7 @@
           <t>17:02
 CD0852
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2330,7 +2330,7 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -2338,15 +2338,15 @@
           <t>11:48
 CD0054
 20:48
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>9:22
+          <t>09:22
 CD5901
 17:40
-8:18</t>
+08:18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2359,7 +2359,7 @@
           <t>12:59
 CD5904
 20:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
@@ -2367,15 +2367,15 @@
           <t>11:48
 CD0055
 21:03
-9:15</t>
+09:15</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2385,18 +2385,18 @@
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2409,7 +2409,7 @@
           <t>12:59
 CD0505
 21:04
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr">
@@ -2417,7 +2417,7 @@
           <t>11:48
 CD0055
 21:03
-9:15</t>
+09:15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2427,10 +2427,10 @@
       </c>
       <c r="T13" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U13" s="1" t="inlineStr">
@@ -2438,7 +2438,7 @@
           <t>13:03
 CD0507
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2448,27 +2448,27 @@
       </c>
       <c r="W13" s="1" t="inlineStr">
         <is>
-          <t>4:41
+          <t>04:41
 CD0067
 12:54
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="X13" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 DO2W
 CD0028
 12:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y13" s="1" t="inlineStr">
         <is>
-          <t>9:33
+          <t>09:33
 CD0055
 17:33
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z13" s="1" t="inlineStr">
@@ -2476,7 +2476,7 @@
           <t>12:50
 CD5901
 21:28
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2491,10 +2491,10 @@
       </c>
       <c r="AC13" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0082
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD13" s="1" t="inlineStr">
@@ -2502,7 +2502,7 @@
           <t>10:00
 CD0083
 19:55
-9:55</t>
+09:55</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
           <t>15:48
 CD0526
 24:30
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -2530,7 +2530,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -2538,7 +2538,7 @@
           <t>17:02
 CD0851
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2553,27 +2553,27 @@
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0074
 12:10
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 DO2W
 CD0027
 14:35
-9:45</t>
+09:45</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>8:45
+          <t>08:45
 CD0046
 16:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2588,34 +2588,34 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>7:08
+          <t>07:08
 CD0045
 16:31
-9:23</t>
+09:23</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2630,42 +2630,42 @@
       </c>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="V14" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0082
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W14" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0078
 13:47
-8:25</t>
+08:25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2680,26 +2680,26 @@
       </c>
       <c r="Z14" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="AA14" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:45
-8:23</t>
+08:23</t>
         </is>
       </c>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0081
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2709,10 +2709,10 @@
       </c>
       <c r="AD14" s="1" t="inlineStr">
         <is>
-          <t>4:52
+          <t>04:52
 CD0088
 12:52
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -2729,10 +2729,10 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>8:45
+          <t>08:45
 CD0046
 16:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2752,18 +2752,18 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0063
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>4:41
+          <t>04:41
 CD0087
 12:54
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2788,18 +2788,18 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>6:53
+          <t>06:53
 CD0032
 14:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -2807,7 +2807,7 @@
           <t>16:04
 CD0531
 25:11
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2815,7 +2815,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2830,18 +2830,18 @@
       </c>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2854,7 +2854,7 @@
           <t>11:16
 CD0051
 20:01
-8:45</t>
+08:45</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2872,7 +2872,7 @@
           <t>10:04
 CD0065
 18:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z15" s="1" t="inlineStr">
@@ -2880,7 +2880,7 @@
           <t>15:12
 CD0562
 25:11
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="AA15" s="1" t="inlineStr">
@@ -2888,7 +2888,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="AB15" s="1" t="inlineStr">
@@ -2896,7 +2896,7 @@
           <t>14:59
 CD0558
 24:21
-9:22</t>
+09:22</t>
         </is>
       </c>
       <c r="AC15" s="1" t="inlineStr">
@@ -2904,7 +2904,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2934,7 +2934,7 @@
           <t>12:01
 CD0554
 20:01
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -2942,7 +2942,7 @@
           <t>15:12
 CD0562
 25:11
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2955,7 +2955,7 @@
           <t>12:00
 CD5902
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
@@ -2963,7 +2963,7 @@
           <t>11:07
 CD5903
 19:08
-8:01</t>
+08:01</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr">
@@ -2972,7 +2972,7 @@
 DO2W
 CD5901
 20:41
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2985,7 +2985,7 @@
           <t>17:02
 CD0543
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -2993,7 +2993,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
@@ -3001,7 +3001,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -3009,7 +3009,7 @@
           <t>12:28
 CD0554
 21:03
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -3017,7 +3017,7 @@
           <t>13:04
 CD0509
 21:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3032,10 +3032,10 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr">
@@ -3043,7 +3043,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr">
@@ -3051,7 +3051,7 @@
           <t>14:59
 CD0513
 24:21
-9:22</t>
+09:22</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -3059,7 +3059,7 @@
           <t>12:28
 CD0554
 21:03
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="V16" s="1" t="inlineStr">
@@ -3067,7 +3067,7 @@
           <t>16:58
 CD0576
 25:25
-8:27</t>
+08:27</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3081,7 +3081,7 @@
 DO2W
 CD0551
 22:08
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y16" s="1" t="inlineStr">
@@ -3089,7 +3089,7 @@
           <t>13:06
 CD5903
 21:06
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z16" s="1" t="inlineStr">
@@ -3097,7 +3097,7 @@
           <t>17:25
 CD0564
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA16" s="1" t="inlineStr">
@@ -3105,7 +3105,7 @@
           <t>17:25
 CD0852
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB16" s="1" t="inlineStr">
@@ -3113,7 +3113,7 @@
           <t>15:04
 CD0512
 23:46
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3143,7 +3143,7 @@
           <t>15:03
 CD0517
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -3151,7 +3151,7 @@
           <t>11:45
 CD0053
 20:27
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3171,27 +3171,27 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0077
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>5:57
+          <t>05:57
 DO2W
 CD0089
 14:54
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3206,18 +3206,18 @@
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3227,18 +3227,18 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0060
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -3253,10 +3253,10 @@
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3266,18 +3266,18 @@
       </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0074
 14:32
-9:42</t>
+09:42</t>
         </is>
       </c>
       <c r="W17" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3287,26 +3287,26 @@
       </c>
       <c r="Y17" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0008
 12:45
-8:46</t>
+08:46</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA17" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3316,18 +3316,18 @@
       </c>
       <c r="AC17" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="AD17" s="1" t="inlineStr">
         <is>
-          <t>4:31
+          <t>04:31
 CD0067
 12:54
-8:23</t>
+08:23</t>
         </is>
       </c>
     </row>
@@ -3344,18 +3344,18 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0065
 13:20
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3365,18 +3365,18 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
@@ -3384,7 +3384,7 @@
           <t>10:07
 CD5902
 19:04
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3404,42 +3404,42 @@
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>08:00
 DSUI
 16:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>08:00
 DSUI
 16:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>08:00
 DSUI
 16:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0078
 13:34
-8:12</t>
+08:12</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3509,10 +3509,10 @@
       </c>
       <c r="AD18" s="1" t="inlineStr">
         <is>
-          <t>6:09
+          <t>06:09
 CD0089
 14:09
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -3554,19 +3554,19 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0023
 12:59
-8:49</t>
+08:49</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 DO2W
 CD0012
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
@@ -3574,7 +3574,7 @@
           <t>10:32
 CD5903
 19:17
-8:45</t>
+08:45</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3589,34 +3589,34 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>4:24
+          <t>04:24
 CD0061
 12:24
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0086
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3631,42 +3631,42 @@
       </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>4:34
+          <t>04:34
 CD0811
 12:54
-8:20</t>
+08:20</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="V19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="W19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0086
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3676,34 +3676,34 @@
       </c>
       <c r="Y19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="Z19" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0017
 12:10
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA19" s="1" t="inlineStr">
         <is>
-          <t>5:09
+          <t>05:09
 CD0032
 14:08
-8:59</t>
+08:59</t>
         </is>
       </c>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3713,10 +3713,10 @@
       </c>
       <c r="AD19" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0012
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
           <t>11:59
 CD0056
 20:59
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -3744,7 +3744,7 @@
           <t>11:48
 CD0055
 20:04
-8:16</t>
+08:16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3762,7 +3762,7 @@
           <t>11:25
 CD5901
 19:32
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
@@ -3770,7 +3770,7 @@
           <t>10:00
 STD2
 18:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -3779,15 +3779,15 @@
 DO2W
 CD0083
 19:45
-9:45</t>
+09:45</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>7:59
+          <t>07:59
 CD5902
 16:06
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3800,15 +3800,15 @@
           <t>11:53
 CD0085
 20:17
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 T
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -3816,7 +3816,7 @@
           <t>11:45
 CD0052
 19:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -3824,7 +3824,7 @@
           <t>10:35
 CD0084
 18:54
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3837,7 +3837,7 @@
           <t>10:59
 CD0050
 18:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr">
@@ -3845,7 +3845,7 @@
           <t>11:45
 CD0053
 20:27
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3855,10 +3855,10 @@
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>6:53
+          <t>06:53
 CD0032
 14:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -3866,7 +3866,7 @@
           <t>11:48
 CD0054
 19:48
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3876,10 +3876,10 @@
       </c>
       <c r="W20" s="1" t="inlineStr">
         <is>
-          <t>8:53
+          <t>08:53
 CD5901
 17:03
-8:10</t>
+08:10</t>
         </is>
       </c>
       <c r="X20" s="1" t="inlineStr">
@@ -3888,7 +3888,7 @@
 DO2W
 CD0056
 20:59
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3911,7 +3911,7 @@
           <t>11:48
 CD0054
 20:17
-8:29</t>
+08:29</t>
         </is>
       </c>
       <c r="AC20" s="1" t="inlineStr">
@@ -3919,7 +3919,7 @@
           <t>11:16
 CD0051
 20:17
-9:01</t>
+09:01</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3941,10 +3941,10 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3954,18 +3954,18 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
@@ -3973,7 +3973,7 @@
           <t>11:06
 CD0033
 21:04
-9:58</t>
+09:58</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
@@ -3981,7 +3981,7 @@
           <t>11:21
 CD5904
 19:40
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3996,51 +3996,51 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DO3W
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -4050,10 +4050,10 @@
       </c>
       <c r="R21" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -4063,18 +4063,18 @@
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V21" s="1" t="inlineStr">
@@ -4082,7 +4082,7 @@
           <t>16:28
 CD0537
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -4096,7 +4096,7 @@
 DO2W
 CD0505
 22:03
-9:04</t>
+09:04</t>
         </is>
       </c>
       <c r="Y21" s="1" t="inlineStr">
@@ -4104,7 +4104,7 @@
           <t>11:45
 CD0053
 20:01
-8:16</t>
+08:16</t>
         </is>
       </c>
       <c r="Z21" s="1" t="inlineStr">
@@ -4112,7 +4112,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4122,18 +4122,18 @@
       </c>
       <c r="AB21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC21" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -4155,26 +4155,26 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0035
 14:54
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4189,43 +4189,43 @@
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0011
 12:37
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>7:08
+          <t>07:08
 DO2W
 CD0045
 16:28
-9:20</t>
+09:20</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:59
-9:12</t>
+09:12</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>5:02
+          <t>05:02
 CD0031
 14:08
-9:06</t>
+09:06</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -4240,18 +4240,18 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0023
 12:59
-8:44</t>
+08:44</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0012
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4261,34 +4261,34 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -4298,35 +4298,35 @@
       </c>
       <c r="W22" s="1" t="inlineStr">
         <is>
-          <t>6:35
+          <t>06:35
 CD0044
 14:59
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="X22" s="1" t="inlineStr">
         <is>
-          <t>6:37
+          <t>06:37
 DO2W
 CD5902
 15:15
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="Y22" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0031
 13:52
-9:42</t>
+09:42</t>
         </is>
       </c>
       <c r="Z22" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 13:15
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -4344,7 +4344,7 @@
           <t>14:04
 CD0516
 22:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD22" s="1" t="inlineStr">
@@ -4352,7 +4352,7 @@
           <t>17:11
 CD0546
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -4369,26 +4369,26 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0028
 12:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>6:03
+          <t>06:03
 CD0039
 14:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>4:34
+          <t>04:34
 CD0032
 12:34
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4403,35 +4403,35 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>6:59
+          <t>06:59
 CD0066
 16:23
-9:24</t>
+09:24</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>4:52
+          <t>04:52
 DO2W
 CD0088
 13:54
-9:02</t>
+09:02</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0060
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0035
 14:54
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4449,7 +4449,7 @@
           <t>15:59
 CD0530
 24:50
-8:51</t>
+08:51</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -4457,7 +4457,7 @@
           <t>14:04
 CD0516
 22:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -4465,7 +4465,7 @@
           <t>16:53
 CD0575
 25:25
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
@@ -4473,7 +4473,7 @@
           <t>17:45
 CD0551
 25:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4486,7 +4486,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="T23" s="1" t="inlineStr">
@@ -4494,7 +4494,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
@@ -4502,7 +4502,7 @@
           <t>15:39
 CD0558
 24:21
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="V23" s="1" t="inlineStr">
@@ -4510,7 +4510,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -4528,7 +4528,7 @@
           <t>14:59
 CD0559
 24:22
-9:23</t>
+09:23</t>
         </is>
       </c>
       <c r="Z23" s="1" t="inlineStr">
@@ -4536,7 +4536,7 @@
           <t>16:21
 CD0513
 24:21
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA23" s="1" t="inlineStr">
@@ -4544,7 +4544,7 @@
           <t>16:28
 CD0571
 25:11
-8:43</t>
+08:43</t>
         </is>
       </c>
       <c r="AB23" s="1" t="inlineStr">
@@ -4552,7 +4552,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC23" s="1" t="inlineStr">
@@ -4560,7 +4560,7 @@
           <t>16:58
 CD0576
 25:25
-8:27</t>
+08:27</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4587,34 +4587,34 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>6:09
+          <t>06:09
 CD0042
 14:45
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0034
 13:54
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4634,42 +4634,42 @@
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>6:03
+          <t>06:03
 CD0039
 14:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M24" s="1" t="inlineStr">
         <is>
-          <t>4:11
+          <t>04:11
 CD0017
 12:51
-8:40</t>
+08:40</t>
         </is>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0066
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4702,7 +4702,7 @@
           <t>15:48
 CD0524
 23:51
-8:03</t>
+08:03</t>
         </is>
       </c>
       <c r="V24" s="1" t="inlineStr">
@@ -4710,7 +4710,7 @@
           <t>13:06
 CD0531
 21:06
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W24" s="1" t="inlineStr">
@@ -4718,7 +4718,7 @@
           <t>12:56
 CD5905
 20:56
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X24" s="1" t="inlineStr">
@@ -4727,7 +4727,7 @@
 DO2W
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -4735,7 +4735,7 @@
           <t>16:22
 CD0553
 25:55
-9:33</t>
+09:33</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -4748,7 +4748,7 @@
           <t>15:12
 CD0562
 23:27
-8:15</t>
+08:15</t>
         </is>
       </c>
       <c r="AB24" s="1" t="inlineStr">
@@ -4756,7 +4756,7 @@
           <t>16:53
 CD0541
 25:25
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="AC24" s="1" t="inlineStr">
@@ -4764,7 +4764,7 @@
           <t>16:28
 CD0537
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4814,7 +4814,7 @@
           <t>17:25
 CD0576
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -4823,7 +4823,7 @@
 DO2W
 CD5902
 23:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4836,7 +4836,7 @@
           <t>14:48
 CD0511
 23:01
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -4844,7 +4844,7 @@
           <t>16:28
 CD0571
 25:11
-8:43</t>
+08:43</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
@@ -4852,7 +4852,7 @@
           <t>15:01
 CD0562
 23:01
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4865,7 +4865,7 @@
           <t>14:55
 CD0557
 22:55
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -4873,7 +4873,7 @@
           <t>12:22
 CD0504
 20:41
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="Q25" s="1" t="inlineStr">
@@ -4881,7 +4881,7 @@
           <t>15:48
 CD0526
 24:30
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="R25" s="1" t="inlineStr">
@@ -4889,7 +4889,7 @@
           <t>15:48
 CD0568
 25:25
-9:37</t>
+09:37</t>
         </is>
       </c>
       <c r="S25" s="1" t="inlineStr">
@@ -4897,7 +4897,7 @@
           <t>17:04
 CD0851
 25:25
-8:21</t>
+08:21</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -4910,7 +4910,7 @@
           <t>17:04
 CD0577
 25:11
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="V25" s="1" t="inlineStr">
@@ -4918,7 +4918,7 @@
           <t>14:00
 CD0556
 22:30
-8:30</t>
+08:30</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -4932,7 +4932,7 @@
 DO2W
 CD0547
 25:25
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="Y25" s="1" t="inlineStr">
@@ -4940,7 +4940,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -4955,26 +4955,26 @@
       </c>
       <c r="AB25" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0073
 13:20
-8:30</t>
+08:30</t>
         </is>
       </c>
       <c r="AC25" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0023
 12:59
-8:44</t>
+08:44</t>
         </is>
       </c>
       <c r="AD25" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
           <t>17:00
 CD0574
 25:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5007,7 +5007,7 @@
           <t>15:21
 CD0564
 25:20
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -5015,7 +5015,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
@@ -5023,7 +5023,7 @@
           <t>15:03
 CD0530
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
@@ -5031,7 +5031,7 @@
           <t>12:53
 CD0516
 21:03
-8:10</t>
+08:10</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5044,7 +5044,7 @@
           <t>12:00
 CD0552
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
@@ -5052,7 +5052,7 @@
           <t>16:07
 CD0532
 25:30
-9:23</t>
+09:23</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -5060,7 +5060,7 @@
           <t>14:37
 CD0562
 22:37
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -5068,7 +5068,7 @@
           <t>15:39
 CD0513
 24:21
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -5086,7 +5086,7 @@
           <t>16:05
 CD0569
 25:25
-9:20</t>
+09:20</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
@@ -5094,7 +5094,7 @@
           <t>17:08
 CD0544
 25:13
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr">
@@ -5102,7 +5102,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -5120,7 +5120,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V26" s="1" t="inlineStr">
@@ -5128,7 +5128,7 @@
           <t>15:23
 CD0566
 23:23
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W26" s="1" t="inlineStr">
@@ -5136,7 +5136,7 @@
           <t>12:00
 CD0504
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X26" s="1" t="inlineStr">
@@ -5145,7 +5145,7 @@
 DO2W
 CD0579
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -5158,7 +5158,7 @@
           <t>14:28
 CD0560
 22:56
-8:28</t>
+08:28</t>
         </is>
       </c>
       <c r="AA26" s="1" t="inlineStr">
@@ -5166,7 +5166,7 @@
           <t>15:51
 CD0528
 23:51
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB26" s="1" t="inlineStr">
@@ -5174,7 +5174,7 @@
           <t>12:28
 CD0554
 21:03
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="AC26" s="1" t="inlineStr">
@@ -5182,7 +5182,7 @@
           <t>16:58
 CD0851
 25:07
-8:09</t>
+08:09</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5207,7 +5207,7 @@
           <t>17:12
 CD0547
 25:25
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5220,7 +5220,7 @@
           <t>14:59
 CD0513
 24:21
-9:22</t>
+09:22</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -5228,7 +5228,7 @@
           <t>11:53
 CD0085
 20:17
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
@@ -5236,7 +5236,7 @@
           <t>15:59
 CD0554
 24:30
-8:31</t>
+08:31</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
@@ -5244,7 +5244,7 @@
           <t>13:15
 CD0509
 21:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5257,7 +5257,7 @@
           <t>17:08
 CD0544
 25:20
-8:12</t>
+08:12</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
@@ -5265,7 +5265,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -5273,7 +5273,7 @@
           <t>17:30
 CD0564
 25:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5288,42 +5288,42 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>6:09
+          <t>06:09
 CD0089
 14:09
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0028
 12:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
-          <t>5:09
+          <t>05:09
 CD0032
 14:08
-8:59</t>
+08:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -5338,43 +5338,43 @@
       </c>
       <c r="V27" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0077
 14:54
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="W27" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0045
 12:32
-8:22</t>
+08:22</t>
         </is>
       </c>
       <c r="X27" s="1" t="inlineStr">
         <is>
-          <t>6:59
+          <t>06:59
 DO2W
 CD5903
 14:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y27" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0039
 12:15
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="Z27" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:35
-9:36</t>
+09:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -5389,18 +5389,18 @@
       </c>
       <c r="AC27" s="1" t="inlineStr">
         <is>
-          <t>5:58
+          <t>05:58
 CD0066
 13:58
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD27" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0078
 13:34
-8:12</t>
+08:12</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
           <t>12:00
 CD0552
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -5428,7 +5428,7 @@
           <t>14:37
 CD0559
 22:37
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -5436,7 +5436,7 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5460,7 +5460,7 @@
 DO2W
 CD5903
 24:28
-9:28</t>
+09:28</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr">
@@ -5468,7 +5468,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -5481,7 +5481,7 @@
           <t>17:04
 CD0851
 25:30
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="M28" s="1" t="inlineStr">
@@ -5489,7 +5489,7 @@
           <t>16:28
 CD0571
 25:02
-8:34</t>
+08:34</t>
         </is>
       </c>
       <c r="N28" s="1" t="inlineStr">
@@ -5497,7 +5497,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -5505,7 +5505,7 @@
           <t>16:50
 CD0533
 24:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -5528,7 +5528,7 @@
           <t>11:53
 CD0085
 20:17
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="T28" s="1" t="inlineStr">
@@ -5536,7 +5536,7 @@
           <t>11:53
 CD0085
 19:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U28" s="1" t="inlineStr">
@@ -5544,7 +5544,7 @@
           <t>14:56
 CD0512
 22:56
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V28" s="1" t="inlineStr">
@@ -5552,7 +5552,7 @@
           <t>10:35
 CD0084
 18:54
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="W28" s="1" t="inlineStr">
@@ -5560,7 +5560,7 @@
           <t>10:00
 CD0083
 18:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -5570,26 +5570,26 @@
       </c>
       <c r="Y28" s="1" t="inlineStr">
         <is>
-          <t>7:59
+          <t>07:59
 CD0042
 17:37
-9:38</t>
+09:38</t>
         </is>
       </c>
       <c r="Z28" s="1" t="inlineStr">
         <is>
-          <t>6:53
+          <t>06:53
 CD0032
 14:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB28" s="1" t="inlineStr">
@@ -5597,7 +5597,7 @@
           <t>11:45
 CD0052
 19:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC28" s="1" t="inlineStr">
@@ -5605,7 +5605,7 @@
           <t>14:55
 CD0557
 22:55
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5635,7 +5635,7 @@
           <t>14:08
 CD0511
 22:08
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -5643,7 +5643,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -5651,7 +5651,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5670,7 +5670,7 @@
 DO2W
 CD0569
 25:30
-9:53</t>
+09:53</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
@@ -5678,7 +5678,7 @@
           <t>15:03
 CD0517
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -5693,26 +5693,26 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0073
 13:20
-8:30</t>
+08:30</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0082
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -5722,18 +5722,18 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0065
 13:20
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -5743,26 +5743,26 @@
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U29" s="1" t="inlineStr">
         <is>
-          <t>4:53
+          <t>04:53
 CD0057
 12:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V29" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0066
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -5777,34 +5777,34 @@
       </c>
       <c r="Y29" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA29" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB29" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5814,10 +5814,10 @@
       </c>
       <c r="AD29" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0086
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -5839,34 +5839,34 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0064
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0073
 14:43
-9:53</t>
+09:53</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5886,18 +5886,18 @@
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -5907,42 +5907,42 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0077
 13:40
-8:18</t>
+08:18</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
-          <t>4:31
+          <t>04:31
 CD0044
 13:34
-9:03</t>
+09:03</t>
         </is>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0064
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -5952,26 +5952,26 @@
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="U30" s="1" t="inlineStr">
         <is>
-          <t>5:09
+          <t>05:09
 CD0033
 13:35
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="V30" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -5981,27 +5981,27 @@
       </c>
       <c r="X30" s="1" t="inlineStr">
         <is>
-          <t>4:41
+          <t>04:41
 DO2W
 CD0068
 13:54
-9:13</t>
+09:13</t>
         </is>
       </c>
       <c r="Y30" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0020
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z30" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0025
 12:54
-8:44</t>
+08:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -6011,18 +6011,18 @@
       </c>
       <c r="AB30" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0063
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC30" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0077
 13:40
-8:18</t>
+08:18</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6049,34 +6049,34 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0008
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6086,35 +6086,35 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>4:41
+          <t>04:41
 DO2W
 CD0067
 12:54
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0028
 12:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -6124,27 +6124,27 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 DO3W
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
-          <t>4:52
+          <t>04:52
 CD0088
 12:52
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -6154,26 +6154,26 @@
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="S31" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -6186,7 +6186,7 @@
           <t>13:25
 CD0516
 23:03
-9:38</t>
+09:38</t>
         </is>
       </c>
       <c r="W31" s="1" t="inlineStr">
@@ -6194,7 +6194,7 @@
           <t>17:11
 CD0546
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X31" s="1" t="inlineStr">
@@ -6203,7 +6203,7 @@
 DO2W
 CD0574
 24:52
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y31" s="1" t="inlineStr">
@@ -6211,7 +6211,7 @@
           <t>14:48
 CD0511
 23:03
-8:15</t>
+08:15</t>
         </is>
       </c>
       <c r="Z31" s="1" t="inlineStr">
@@ -6219,7 +6219,7 @@
           <t>15:07
 CD5902
 23:27
-8:20</t>
+08:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -6237,7 +6237,7 @@
           <t>15:03
 CD0566
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD31" s="1" t="inlineStr">
@@ -6245,7 +6245,7 @@
           <t>12:22
 CD0504
 20:41
-8:19</t>
+08:19</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
           <t>16:25
 CD0570
 25:00
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6278,7 +6278,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
@@ -6286,7 +6286,7 @@
           <t>15:12
 CD0562
 25:11
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -6294,7 +6294,7 @@
           <t>17:04
 CD0558
 25:25
-8:21</t>
+08:21</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6308,7 +6308,7 @@
 DO2W
 CD0546
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr">
@@ -6316,7 +6316,7 @@
           <t>17:55
 CD0551
 25:55
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -6329,7 +6329,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M32" s="1" t="inlineStr">
@@ -6337,15 +6337,15 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -6353,7 +6353,7 @@
           <t>16:28
 CD0537
 25:30
-9:02</t>
+09:02</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -6366,7 +6366,7 @@
           <t>12:00
 CD0552
 20:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr">
@@ -6374,7 +6374,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="inlineStr">
@@ -6382,7 +6382,7 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -6400,7 +6400,7 @@
           <t>16:13
 CD0533
 24:30
-8:17</t>
+08:17</t>
         </is>
       </c>
       <c r="W32" s="1" t="inlineStr">
@@ -6408,7 +6408,7 @@
           <t>15:45
 CD0567
 24:50
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="X32" s="1" t="inlineStr">
@@ -6417,7 +6417,7 @@
 DO2W
 CD0550
 23:35
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y32" s="1" t="inlineStr">
@@ -6425,7 +6425,7 @@
           <t>17:12
 CD0532
 25:35
-8:23</t>
+08:23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -6438,7 +6438,7 @@
           <t>16:50
 CD0851
 24:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB32" s="1" t="inlineStr">
@@ -6446,7 +6446,7 @@
           <t>15:48
 CD0524
 23:51
-8:03</t>
+08:03</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -6456,10 +6456,10 @@
       </c>
       <c r="AD32" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0013
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
     </row>
@@ -6479,30 +6479,45 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NGRSN</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>NGRSN</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>NGRSN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NGRSN</t>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>-
+NGRSN
+-
+-</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>-
+NGRSN
+-
+-</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>-
+NGRSN
+-
+-</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>-
+NGRSN
+-
+-</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>DO3W
-NGRSN</t>
+          <t>-
+DO3W
+NGRSN
+-
+-</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -6553,42 +6568,42 @@
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="T33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="U33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -6603,43 +6618,43 @@
       </c>
       <c r="Y33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DO3W
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="Z33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AA33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AB33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AC33" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 NGRSD
 17:30
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6664,7 +6679,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6674,10 +6689,10 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -6685,7 +6700,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -6693,7 +6708,7 @@
           <t>16:46
 CD0512
 24:46
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
@@ -6701,7 +6716,7 @@
           <t>16:13
 CD0570
 24:50
-8:37</t>
+08:37</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -6721,10 +6736,10 @@
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M34" s="1" t="inlineStr">
@@ -6732,7 +6747,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="N34" s="1" t="inlineStr">
@@ -6740,7 +6755,7 @@
           <t>13:03
 CD0507
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -6748,7 +6763,7 @@
           <t>14:00
 CD0556
 22:55
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -6771,7 +6786,7 @@
           <t>17:25
 CD0564
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T34" s="1" t="inlineStr">
@@ -6779,7 +6794,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="U34" s="1" t="inlineStr">
@@ -6787,7 +6802,7 @@
           <t>17:25
 CD0578
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V34" s="1" t="inlineStr">
@@ -6795,7 +6810,7 @@
           <t>15:00
 CD0557
 24:30
-9:30</t>
+09:30</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -6809,7 +6824,7 @@
 DO2W
 CD0570
 24:52
-8:27</t>
+08:27</t>
         </is>
       </c>
       <c r="Y34" s="1" t="inlineStr">
@@ -6817,7 +6832,7 @@
           <t>17:22
 CD5905
 25:55
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -6832,26 +6847,26 @@
       </c>
       <c r="AB34" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0034
 13:54
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="AC34" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0011
 12:37
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="AD34" s="1" t="inlineStr">
         <is>
-          <t>4:31
+          <t>04:31
 CD0044
 13:34
-9:03</t>
+09:03</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6886,7 @@
           <t>17:08
 CD0544
 25:13
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -6879,7 +6894,7 @@
           <t>16:50
 CD0851
 24:50
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6897,7 +6912,7 @@
           <t>16:50
 CD0577
 25:01
-8:11</t>
+08:11</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
@@ -6905,7 +6920,7 @@
           <t>16:28
 CD0537
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
@@ -6914,7 +6929,7 @@
 DO2W
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr">
@@ -6922,7 +6937,7 @@
           <t>13:04
 CD0505
 21:04
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K35" s="1" t="inlineStr">
@@ -6930,7 +6945,7 @@
           <t>11:45
 CD0053
 20:27
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -6953,7 +6968,7 @@
           <t>16:58
 CD0851
 25:07
-8:09</t>
+08:09</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -6966,7 +6981,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr">
@@ -6974,7 +6989,7 @@
           <t>12:12
 CD0553
 20:27
-8:15</t>
+08:15</t>
         </is>
       </c>
       <c r="S35" s="1" t="inlineStr">
@@ -6982,7 +6997,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="T35" s="1" t="inlineStr">
@@ -6990,7 +7005,7 @@
           <t>17:02
 CD0851
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -7005,35 +7020,35 @@
       </c>
       <c r="W35" s="1" t="inlineStr">
         <is>
-          <t>4:10
+          <t>04:10
 CD0018
 12:47
-8:37</t>
+08:37</t>
         </is>
       </c>
       <c r="X35" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 DO2W
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="Y35" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0035
 14:28
-9:06</t>
+09:06</t>
         </is>
       </c>
       <c r="Z35" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -7048,18 +7063,18 @@
       </c>
       <c r="AC35" s="1" t="inlineStr">
         <is>
-          <t>8:00
+          <t>08:00
 TTC1
 16:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD35" s="1" t="inlineStr">
         <is>
-          <t>7:08
+          <t>07:08
 CD0045
 16:31
-9:23</t>
+09:23</t>
         </is>
       </c>
     </row>
@@ -7076,10 +7091,10 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0060
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7089,18 +7104,18 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 13:22
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7110,51 +7125,51 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 DO2W
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0008
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0068
 13:54
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -7164,18 +7179,18 @@
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0074
 14:32
-9:42</t>
+09:42</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
-          <t>4:31
+          <t>04:31
 CD0067
 12:54
-8:23</t>
+08:23</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -7185,18 +7200,18 @@
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
-          <t>6:03
+          <t>06:03
 CD0039
 14:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -7206,43 +7221,43 @@
       </c>
       <c r="U36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="V36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="W36" s="1" t="inlineStr">
         <is>
-          <t>4:52
+          <t>04:52
 CD0088
 12:52
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X36" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 DO2W
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y36" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -7260,7 +7275,7 @@
           <t>17:25
 CD0578
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
@@ -7268,7 +7283,7 @@
           <t>16:13
 CD0533
 24:30
-8:17</t>
+08:17</t>
         </is>
       </c>
       <c r="AD36" s="1" t="inlineStr">
@@ -7276,7 +7291,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7311,7 @@
           <t>17:45
 CD0551
 25:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -7304,7 +7319,7 @@
           <t>16:07
 CD0532
 25:25
-9:18</t>
+09:18</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -7312,7 +7327,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -7320,7 +7335,7 @@
           <t>16:28
 CD0571
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7339,7 +7354,7 @@
 DO2W
 CD5905
 25:50
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr">
@@ -7347,7 +7362,7 @@
           <t>15:41
 CD0570
 23:41
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K37" s="1" t="inlineStr">
@@ -7355,7 +7370,7 @@
           <t>15:48
 CD0568
 24:50
-9:02</t>
+09:02</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -7373,7 +7388,7 @@
           <t>15:39
 CD0558
 24:21
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -7381,7 +7396,7 @@
           <t>15:03
 CD0566
 23:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -7389,7 +7404,7 @@
           <t>16:48
 CD0573
 25:07
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="Q37" s="1" t="inlineStr">
@@ -7397,7 +7412,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -7407,10 +7422,10 @@
       </c>
       <c r="S37" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T37" s="1" t="inlineStr">
@@ -7418,7 +7433,7 @@
           <t>15:12
 CD0562
 25:11
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="U37" s="1" t="inlineStr">
@@ -7426,7 +7441,7 @@
           <t>15:59
 CD0530
 24:50
-8:51</t>
+08:51</t>
         </is>
       </c>
       <c r="V37" s="1" t="inlineStr">
@@ -7434,7 +7449,7 @@
           <t>16:25
 CD0570
 25:00
-8:35</t>
+08:35</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -7449,34 +7464,34 @@
       </c>
       <c r="Y37" s="1" t="inlineStr">
         <is>
-          <t>9:59
+          <t>09:59
 CD5901
 17:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Z37" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA37" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB37" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 13:47
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -7508,34 +7523,34 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0059
 12:54
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0081
 15:08
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7549,7 +7564,7 @@
 DO2W
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J38" s="1" t="inlineStr">
@@ -7557,7 +7572,7 @@
           <t>17:12
 CD0547
 25:20
-8:08</t>
+08:08</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -7565,7 +7580,7 @@
           <t>17:26
 CD0553
 25:30
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -7585,10 +7600,10 @@
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -7601,7 +7616,7 @@
           <t>17:45
 CD0550
 25:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R38" s="1" t="inlineStr">
@@ -7609,7 +7624,7 @@
           <t>16:07
 CD0532
 25:25
-9:18</t>
+09:18</t>
         </is>
       </c>
       <c r="S38" s="1" t="inlineStr">
@@ -7617,7 +7632,7 @@
           <t>16:28
 CD0571
 25:11
-8:43</t>
+08:43</t>
         </is>
       </c>
       <c r="T38" s="1" t="inlineStr">
@@ -7625,7 +7640,7 @@
           <t>15:21
 CD0564
 25:20
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -7643,7 +7658,7 @@
           <t>16:48
 CD0573
 25:07
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="X38" s="1" t="inlineStr">
@@ -7652,7 +7667,7 @@
 DO2W
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y38" s="1" t="inlineStr">
@@ -7660,7 +7675,7 @@
           <t>16:08
 CD5904
 25:35
-9:27</t>
+09:27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -7673,7 +7688,7 @@
           <t>17:25
 CD0564
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -7691,7 +7706,7 @@
           <t>15:45
 CD0567
 24:50
-9:05</t>
+09:05</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7731,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -7724,7 +7739,7 @@
           <t>15:01
 CD0571
 23:01
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -7732,7 +7747,7 @@
           <t>15:21
 CD0564
 25:20
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
@@ -7740,7 +7755,7 @@
           <t>16:48
 CD0541
 25:25
-8:37</t>
+08:37</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7754,7 +7769,7 @@
 DO2W
 CD5904
 25:50
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="J39" s="1" t="inlineStr">
@@ -7762,7 +7777,7 @@
           <t>17:35
 CD0550
 25:35
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -7772,10 +7787,10 @@
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M39" s="1" t="inlineStr">
@@ -7783,7 +7798,7 @@
           <t>17:04
 CD0851
 25:30
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="N39" s="1" t="inlineStr">
@@ -7791,7 +7806,7 @@
           <t>16:21
 CD0541
 24:21
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -7799,7 +7814,7 @@
           <t>16:25
 CD0570
 24:30
-8:05</t>
+08:05</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -7812,7 +7827,7 @@
           <t>17:25
 CD0579
 25:25
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr">
@@ -7820,7 +7835,7 @@
           <t>14:08
 CD0511
 22:08
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="inlineStr">
@@ -7828,7 +7843,7 @@
           <t>15:01
 CD0562
 23:01
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T39" s="1" t="inlineStr">
@@ -7836,7 +7851,7 @@
           <t>16:28
 CD0571
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -7854,7 +7869,7 @@
           <t>16:05
 CD0569
 25:25
-9:20</t>
+09:20</t>
         </is>
       </c>
       <c r="X39" s="1" t="inlineStr">
@@ -7863,7 +7878,7 @@
 DO2W
 CD0526
 24:32
-8:44</t>
+08:44</t>
         </is>
       </c>
       <c r="Y39" s="1" t="inlineStr">
@@ -7871,7 +7886,7 @@
           <t>14:25
 CD0543
 23:41
-9:16</t>
+09:16</t>
         </is>
       </c>
       <c r="Z39" s="1" t="inlineStr">
@@ -7879,7 +7894,7 @@
           <t>15:58
 CD0528
 24:50
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="AA39" s="1" t="inlineStr">
@@ -7887,7 +7902,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -7902,10 +7917,10 @@
       </c>
       <c r="AD39" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0027
 14:35
-9:45</t>
+09:45</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7945,7 @@
           <t>12:12
 CD0553
 20:27
-8:15</t>
+08:15</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -7938,7 +7953,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -7946,7 +7961,7 @@
           <t>14:59
 CD0513
 24:21
-9:22</t>
+09:22</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -7954,7 +7969,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -7968,7 +7983,7 @@
 DO2W
 CD0504
 25:30
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr">
@@ -7976,7 +7991,7 @@
           <t>17:35
 CD0526
 25:35
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -7986,10 +8001,10 @@
       </c>
       <c r="L40" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M40" s="1" t="inlineStr">
@@ -7997,7 +8012,7 @@
           <t>15:00
 CD0560
 24:21
-9:21</t>
+09:21</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -8005,7 +8020,7 @@
           <t>14:56
 CD0512
 22:56
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -8038,7 +8053,7 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -8051,7 +8066,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W40" s="1" t="inlineStr">
@@ -8059,7 +8074,7 @@
           <t>16:53
 CD0575
 25:25
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="X40" s="1" t="inlineStr">
@@ -8068,7 +8083,7 @@
 DO2W
 CD0517
 24:32
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -8081,7 +8096,7 @@
           <t>16:28
 CD0571
 25:25
-8:57</t>
+08:57</t>
         </is>
       </c>
       <c r="AA40" s="1" t="inlineStr">
@@ -8089,7 +8104,7 @@
           <t>16:21
 CD0513
 24:21
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB40" s="1" t="inlineStr">
@@ -8097,7 +8112,7 @@
           <t>17:04
 CD0577
 25:11
-8:07</t>
+08:07</t>
         </is>
       </c>
       <c r="AC40" s="1" t="inlineStr">
@@ -8105,7 +8120,7 @@
           <t>14:00
 CD0556
 22:55
-8:55</t>
+08:55</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -8130,7 +8145,7 @@
           <t>17:45
 CD0550
 25:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -8138,7 +8153,7 @@
           <t>15:48
 CD0568
 25:25
-9:37</t>
+09:37</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -8156,7 +8171,7 @@
           <t>15:48
 CD0524
 25:01
-9:13</t>
+09:13</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
@@ -8164,7 +8179,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
@@ -8173,7 +8188,7 @@
 DO2W
 CD0575
 25:30
-8:37</t>
+08:37</t>
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr">
@@ -8181,7 +8196,7 @@
           <t>17:27
 CD0579
 25:55
-8:28</t>
+08:28</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -8194,7 +8209,7 @@
           <t>15:39
 CD0513
 24:21
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="M41" s="1" t="inlineStr">
@@ -8202,7 +8217,7 @@
           <t>15:21
 CD0564
 25:20
-9:59</t>
+09:59</t>
         </is>
       </c>
       <c r="N41" s="1" t="inlineStr">
@@ -8210,7 +8225,7 @@
           <t>17:02
 CD0851
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -8218,7 +8233,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -8231,15 +8246,15 @@
           <t>11:59
 CD0056
 20:59
-9:00</t>
+09:00</t>
         </is>
       </c>
       <c r="R41" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 DS
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -8254,35 +8269,35 @@
       </c>
       <c r="U41" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0073
 13:20
-8:30</t>
+08:30</t>
         </is>
       </c>
       <c r="V41" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0023
 12:59
-8:44</t>
+08:44</t>
         </is>
       </c>
       <c r="W41" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0012
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="X41" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 DO2W
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -8292,34 +8307,34 @@
       </c>
       <c r="Z41" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA41" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0061
 12:15
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB41" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="AC41" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -8341,34 +8356,34 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8383,19 +8398,19 @@
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 DO2W
 CD0013
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>8:59
+          <t>08:59
 CD0050
 17:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -8405,26 +8420,26 @@
       </c>
       <c r="L42" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
-          <t>4:11
+          <t>04:11
 CD0811
 12:54
-8:43</t>
+08:43</t>
         </is>
       </c>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0081
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -8434,42 +8449,42 @@
       </c>
       <c r="P42" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0027
 14:35
-9:45</t>
+09:45</t>
         </is>
       </c>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr">
         <is>
-          <t>6:09
+          <t>06:09
 CD0042
 14:45
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="S42" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0079
 14:49
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 M
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -8484,19 +8499,19 @@
       </c>
       <c r="W42" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0013
 13:14
-9:15</t>
+09:15</t>
         </is>
       </c>
       <c r="X42" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 DO2W
 CD0060
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -8506,26 +8521,26 @@
       </c>
       <c r="Z42" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0075
 14:54
-9:32</t>
+09:32</t>
         </is>
       </c>
       <c r="AA42" s="1" t="inlineStr">
         <is>
-          <t>4:50
+          <t>04:50
 CD0025
 12:54
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="AB42" s="1" t="inlineStr">
         <is>
-          <t>5:09
+          <t>05:09
 CD0033
 13:35
-8:26</t>
+08:26</t>
         </is>
       </c>
       <c r="AC42" s="1" t="inlineStr">
@@ -8533,7 +8548,7 @@
           <t>10:35
 CD0084
 18:54
-8:19</t>
+08:19</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -8555,10 +8570,10 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8573,43 +8588,43 @@
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>4:53
+          <t>04:53
 CD0057
 12:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>4:47
+          <t>04:47
 CD0087
 12:47
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 DO2W
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>9:36
+          <t>09:36
 CD0056
 18:00
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -8619,34 +8634,34 @@
       </c>
       <c r="L43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:32
-8:33</t>
+08:33</t>
         </is>
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0001
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>5:22
+          <t>05:22
 CD0034
 13:54
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -8661,18 +8676,18 @@
       </c>
       <c r="R43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="S43" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0017
 12:51
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -8682,35 +8697,35 @@
       </c>
       <c r="U43" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0018
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="V43" s="1" t="inlineStr">
         <is>
-          <t>4:53
+          <t>04:53
 CD0011
 12:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W43" s="1" t="inlineStr">
         <is>
-          <t>6:49
+          <t>06:49
 CD0089
 16:43
-9:54</t>
+09:54</t>
         </is>
       </c>
       <c r="X43" s="1" t="inlineStr">
         <is>
-          <t>5:28
+          <t>05:28
 DO2W
 CD5901
 13:28
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -8720,34 +8735,34 @@
       </c>
       <c r="Z43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0002
 11:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0057
 12:37
-8:38</t>
+08:38</t>
         </is>
       </c>
       <c r="AB43" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 12:40
-8:41</t>
+08:41</t>
         </is>
       </c>
       <c r="AC43" s="1" t="inlineStr">
         <is>
-          <t>4:00
+          <t>04:00
 STD1
 12:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -8774,34 +8789,34 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>4:15
+          <t>04:15
 CD0020
 12:47
-8:32</t>
+08:32</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>4:53
+          <t>04:53
 CD0057
 12:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>6:53
+          <t>06:53
 CD0032
 14:53
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0007
 13:40
-9:41</t>
+09:41</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -8811,19 +8826,19 @@
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 DO2W
 CD0086
 12:03
-8:04</t>
+08:04</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>3:59
+          <t>03:59
 CD0010
 12:35
-8:36</t>
+08:36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -8833,26 +8848,26 @@
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
-          <t>5:09
+          <t>05:09
 CD0032
 14:08
-8:59</t>
+08:59</t>
         </is>
       </c>
       <c r="M44" s="1" t="inlineStr">
         <is>
-          <t>4:11
+          <t>04:11
 CD0057
 13:03
-8:52</t>
+08:52</t>
         </is>
       </c>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>8:30
+          <t>08:30
 OGT3
 17:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -8865,7 +8880,7 @@
           <t>17:11
 CD0546
 25:11
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="Q44" s="1" t="inlineStr">
@@ -8873,7 +8888,7 @@
           <t>17:00
 CD0574
 25:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -8886,7 +8901,7 @@
           <t>15:39
 CD0513
 24:21
-8:42</t>
+08:42</t>
         </is>
       </c>
       <c r="T44" s="1" t="inlineStr">
@@ -8894,7 +8909,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="U44" s="1" t="inlineStr">
@@ -8902,7 +8917,7 @@
           <t>17:02
 CD0851
 25:02
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -8915,7 +8930,7 @@
           <t>11:53
 CD5904
 20:03
-8:10</t>
+08:10</t>
         </is>
       </c>
       <c r="X44" s="1" t="inlineStr">
@@ -8924,7 +8939,7 @@
 DO2W
 CD0050
 20:04
-9:05</t>
+09:05</t>
         </is>
       </c>
       <c r="Y44" s="1" t="inlineStr">
@@ -8932,7 +8947,7 @@
           <t>12:50
 CD5902
 21:04
-8:14</t>
+08:14</t>
         </is>
       </c>
       <c r="Z44" s="1" t="inlineStr">
@@ -8940,7 +8955,7 @@
           <t>13:00
 TTC1
 21:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -8958,7 +8973,7 @@
           <t>16:04
 CD0531
 25:11
-9:07</t>
+09:07</t>
         </is>
       </c>
       <c r="AD44" s="1" t="inlineStr">
@@ -8966,7 +8981,7 @@
           <t>16:48
 CD0573
 25:07
-8:19</t>
+08:19</t>
         </is>
       </c>
     </row>

--- a/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
@@ -847,21 +847,17 @@
           <t>12:59
 CD0505
 21:04
-8:05</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+08:05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -869,7 +865,7 @@
           <t>10:00
 STD2
 18:00
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -877,7 +873,7 @@
           <t>12:59
 CD0578
 20:59
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
@@ -885,29 +881,22 @@
           <t>10:25
 CD0084
 18:54
-8:29</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+08:29</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -915,7 +904,7 @@
           <t>13:03
 CD0506
 21:03
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
@@ -923,7 +912,7 @@
           <t>11:53
 CD0085
 20:17
-8:24</t>
+08:24</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
@@ -931,14 +920,12 @@
           <t>15:48
 CD0524
 23:51
-8:03</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+08:03</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -946,7 +933,7 @@
           <t>10:00
 CD0083
 19:55
-9:55</t>
+09:55</t>
         </is>
       </c>
       <c r="Q6" s="1" t="inlineStr">
@@ -954,7 +941,7 @@
           <t>17:12
 CD0547
 25:25
-8:13</t>
+08:13</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr">
@@ -962,21 +949,17 @@
           <t>15:39
 CD0559
 24:50
-9:11</t>
-        </is>
-      </c>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+09:11</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U6" s="1" t="inlineStr">
@@ -984,15 +967,15 @@
           <t>11:45
 CD0052
 19:45
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="V6" s="1" t="inlineStr">
         <is>
-          <t>7:30
+          <t>07:30
 OGC4
 15:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="W6" s="1" t="inlineStr">
@@ -1000,28 +983,22 @@
           <t>11:51
 CD5903
 19:51
-8:00</t>
-        </is>
-      </c>
-      <c r="X6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+08:00</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA6" s="1" t="inlineStr">
@@ -1029,7 +1006,7 @@
           <t>11:33
 CD0085
 19:33
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AB6" s="1" t="inlineStr">
@@ -1037,7 +1014,7 @@
           <t>13:21
 CD0507
 22:56
-9:35</t>
+09:35</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
@@ -1045,7 +1022,7 @@
           <t>15:30
 STD3
 23:30
-8:00</t>
+08:00</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr">
@@ -1053,7 +1030,7 @@
           <t>16:53
 CD0575
 25:25
-8:32</t>
+08:32</t>
         </is>
       </c>
     </row>

--- a/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TD.xlsx
@@ -1787,9 +1787,9 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>08:30
+          <t>08:00
 M
-17:30
+16:00
 08:00</t>
         </is>
       </c>
@@ -4040,9 +4040,9 @@
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>08:30
+          <t>08:00
 M
-17:30
+16:00
 08:00</t>
         </is>
       </c>
@@ -6456,45 +6456,30 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>-
-NGRSN
--
--</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>-
-NGRSN
--
--</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>-
-NGRSN
--
--</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>-
-NGRSN
--
--</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NGRSN</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>-
-DO3W
-NGRSN
--
--</t>
+          <t>DO3W
+NGRSN</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -8458,9 +8443,9 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>08:30
+          <t>08:00
 M
-17:30
+16:00
 08:00</t>
         </is>
       </c>
